--- a/Result/profitability/5223.xlsx
+++ b/Result/profitability/5223.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM44"/>
+  <dimension ref="A1:AM45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6022,6 +6022,133 @@
         <v>115.1</v>
       </c>
     </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>5223</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>485</v>
+      </c>
+      <c r="D45" t="n">
+        <v>411</v>
+      </c>
+      <c r="E45" t="n">
+        <v>73</v>
+      </c>
+      <c r="F45" t="n">
+        <v>15.12</v>
+      </c>
+      <c r="G45" t="n">
+        <v>-3</v>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>-0.63%</t>
+        </is>
+      </c>
+      <c r="I45" t="n">
+        <v>-2</v>
+      </c>
+      <c r="J45" t="n">
+        <v>-5</v>
+      </c>
+      <c r="K45" t="n">
+        <v>-10</v>
+      </c>
+      <c r="L45" t="n">
+        <v>-0.23</v>
+      </c>
+      <c r="M45" t="n">
+        <v>-0.1575</v>
+      </c>
+      <c r="N45" t="n">
+        <v>16.0475</v>
+      </c>
+      <c r="O45" t="n">
+        <v>0</v>
+      </c>
+      <c r="P45" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>0</v>
+      </c>
+      <c r="R45" t="n">
+        <v>0</v>
+      </c>
+      <c r="S45" t="n">
+        <v>0</v>
+      </c>
+      <c r="T45" t="n">
+        <v>0</v>
+      </c>
+      <c r="U45" t="n">
+        <v>0</v>
+      </c>
+      <c r="V45" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W45" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="X45" t="n">
+        <v>-0.4772727272727273</v>
+      </c>
+      <c r="Y45" t="n">
+        <v>1.899999999999999</v>
+      </c>
+      <c r="Z45" t="n">
+        <v>0.1437216338880483</v>
+      </c>
+      <c r="AA45" t="n">
+        <v>-0.3</v>
+      </c>
+      <c r="AB45" t="n">
+        <v>-4.285714285714286</v>
+      </c>
+      <c r="AC45" t="n">
+        <v>0.4599999999999991</v>
+      </c>
+      <c r="AD45" t="n">
+        <v>0.03137789904502042</v>
+      </c>
+      <c r="AE45" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH45" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ45" t="inlineStr">
+        <is>
+          <t>EPS衰退 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK45" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL45" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM45" t="n">
+        <v>115.2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
